--- a/GameConfig/Datas/__tables__.xlsx
+++ b/GameConfig/Datas/__tables__.xlsx
@@ -1331,6 +1331,43 @@
       <x:c r="K16"/>
       <x:c r="L16"/>
     </x:row>
+    <x:row r="17" ht="24" customHeight="1">
+      <x:c r="A17" s="1"/>
+      <x:c r="B17" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">skill.TbSkill</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C17" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Skill</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D17" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E17" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">skill.xlsx</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F17" s="1"/>
+      <x:c r="G17" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">map</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H17" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">c</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I17" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">技能配置</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/GameConfig/Datas/__tables__.xlsx
+++ b/GameConfig/Datas/__tables__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfd65e14e1f1645e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf70cbd12283b4393"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1368,6 +1368,34 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="18">
+      <x:c r="A18"/>
+      <x:c r="B18" t="str">
+        <x:v>skill.TbSkillLevel</x:v>
+      </x:c>
+      <x:c r="C18" t="str">
+        <x:v>SkillLevel</x:v>
+      </x:c>
+      <x:c r="D18" s="2" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E18" t="str">
+        <x:v>skilllevel.xlsx</x:v>
+      </x:c>
+      <x:c r="F18"/>
+      <x:c r="G18" t="str">
+        <x:v>map</x:v>
+      </x:c>
+      <x:c r="H18" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="I18" t="str">
+        <x:v>技能等级配置</x:v>
+      </x:c>
+      <x:c r="J18"/>
+      <x:c r="K18"/>
+      <x:c r="L18"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/GameConfig/Datas/__tables__.xlsx
+++ b/GameConfig/Datas/__tables__.xlsx
@@ -903,435 +903,546 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="2" max="2" width="20.380952835083008" customWidth="1"/>
-    <x:col min="3" max="3" width="15.571428298950195" customWidth="1"/>
-    <x:col min="4" max="4" width="32.42856979370117" customWidth="1"/>
-    <x:col min="5" max="5" width="24.380952835083008" customWidth="1"/>
-    <x:col min="6" max="9" width="18" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" s="1" customFormat="1">
-      <x:c r="A1" s="1" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B1" s="1" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C1" s="1" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D1" s="1" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E1" s="1" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F1" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G1" s="1" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H1" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I1" s="1" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J1" s="1" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K1" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" s="1" customFormat="1">
-      <x:c r="A2" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="E2" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G2" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H2" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="I2" s="1" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="K2" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" s="1" customFormat="1">
-      <x:c r="A3" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D3" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="E3" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F3" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="G3" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="H3" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="K3" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="B4" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C4" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D4" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E4" t="s">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="B5" s="3" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C5" s="3" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="D5" s="3" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E5" s="3" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6"/>
-      <x:c r="B6" t="str">
-        <x:v>robot.TbRobot</x:v>
-      </x:c>
-      <x:c r="C6" t="str">
-        <x:v>Robot</x:v>
-      </x:c>
-      <x:c r="D6" s="2" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E6" t="str">
-        <x:v>robot.xlsx</x:v>
-      </x:c>
-      <x:c r="F6"/>
-      <x:c r="G6" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H6" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I6" t="str">
-        <x:v>机器人</x:v>
-      </x:c>
-      <x:c r="J6"/>
-      <x:c r="K6"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7"/>
-      <x:c r="B7" t="str">
-        <x:v>robot.TbRobotShape</x:v>
-      </x:c>
-      <x:c r="C7" t="str">
-        <x:v>RobotShape</x:v>
-      </x:c>
-      <x:c r="D7" s="2" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E7" t="str">
-        <x:v>robot_shape.xlsx</x:v>
-      </x:c>
-      <x:c r="F7"/>
-      <x:c r="G7" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H7" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I7" t="str">
-        <x:v>机器人占格形状</x:v>
-      </x:c>
-      <x:c r="J7"/>
-      <x:c r="K7"/>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8"/>
-      <x:c r="B8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">drop.TbDrop</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Drop</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D8" s="2" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">drop.xlsx</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F8"/>
-      <x:c r="G8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">map</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">c</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">掉落配置</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J8"/>
-      <x:c r="K8"/>
-    </x:row>
-    <x:row r="9" ht="24" customHeight="1">
-      <x:c r="A9" s="1"/>
-      <x:c r="B9" s="1" t="str">
-        <x:v>glass.TbGlass</x:v>
-      </x:c>
-      <x:c r="C9" s="1" t="str">
-        <x:v>Glass</x:v>
-      </x:c>
-      <x:c r="D9" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E9" s="1" t="str">
-        <x:v>glass.xlsx</x:v>
-      </x:c>
-      <x:c r="F9" s="1"/>
-      <x:c r="G9" s="1" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H9" s="1" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I9" s="1" t="str">
-        <x:v>玻璃配置</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="24" customHeight="1">
-      <x:c r="A10" s="1"/>
-      <x:c r="B10" s="1" t="str">
-        <x:v>board.TbBoardLayout</x:v>
-      </x:c>
-      <x:c r="C10" s="1" t="str">
-        <x:v>BoardLayout</x:v>
-      </x:c>
-      <x:c r="D10" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E10" s="1" t="str">
-        <x:v>board_layout.xlsx</x:v>
-      </x:c>
-      <x:c r="F10" s="1"/>
-      <x:c r="G10" s="1" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H10" s="1" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I10" s="1" t="str">
-        <x:v>棋盘布局配置</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11"/>
-      <x:c r="B11" t="str">
-        <x:v>enemy.TbEnemy</x:v>
-      </x:c>
-      <x:c r="C11" t="str">
-        <x:v>Enemy</x:v>
-      </x:c>
-      <x:c r="D11" s="2" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E11" t="str">
-        <x:v>enemy.xlsx</x:v>
-      </x:c>
-      <x:c r="F11"/>
-      <x:c r="G11" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H11" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I11" t="str">
-        <x:v>敌人配置</x:v>
-      </x:c>
-      <x:c r="J11"/>
-      <x:c r="K11"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="B12" t="str">
-        <x:v>tower.TbTower</x:v>
-      </x:c>
-      <x:c r="C12" t="str">
-        <x:v>Tower</x:v>
-      </x:c>
-      <x:c r="D12" s="2" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E12" t="str">
-        <x:v>tower.xlsx</x:v>
-      </x:c>
-      <x:c r="F12"/>
-      <x:c r="G12" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H12" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I12" t="str">
-        <x:v>防御塔配置</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="B13" t="str">
-        <x:v>wave.TbWaveSpawn</x:v>
-      </x:c>
-      <x:c r="C13" t="str">
-        <x:v>WaveSpawn</x:v>
-      </x:c>
-      <x:c r="D13" s="2" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E13" t="str">
-        <x:v>wave_spawn.xlsx</x:v>
-      </x:c>
-      <x:c r="F13"/>
-      <x:c r="G13" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H13" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I13" t="str">
-        <x:v>波次出兵配置</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="42" customHeight="1">
-      <x:c r="A14"/>
-      <x:c r="B14" t="str">
-        <x:v>item.TbItemBase</x:v>
-      </x:c>
-      <x:c r="C14" t="str">
-        <x:v>ItemBase</x:v>
-      </x:c>
-      <x:c r="D14" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E14" t="str">
-        <x:v>item_base.xlsx</x:v>
-      </x:c>
-      <x:c r="F14"/>
-      <x:c r="G14" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H14" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I14" t="str">
-        <x:v>道具基础表</x:v>
-      </x:c>
-      <x:c r="J14"/>
-      <x:c r="K14"/>
-    </x:row>
-    <x:row r="15" ht="42" customHeight="1">
-      <x:c r="A15"/>
-      <x:c r="B15" t="str">
-        <x:v>settlement.TbResultAward</x:v>
-      </x:c>
-      <x:c r="C15" t="str">
-        <x:v>ResultAward</x:v>
-      </x:c>
-      <x:c r="D15" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E15" t="str">
-        <x:v>result_award.xlsx</x:v>
-      </x:c>
-      <x:c r="F15"/>
-      <x:c r="G15" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H15" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I15" t="str">
-        <x:v>结算奖励表</x:v>
-      </x:c>
-      <x:c r="J15"/>
-      <x:c r="K15"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16"/>
-      <x:c r="B16" t="str">
-        <x:v>wave.TbWavePlan</x:v>
-      </x:c>
-      <x:c r="C16" t="str">
-        <x:v>WavePlan</x:v>
-      </x:c>
-      <x:c r="D16" s="2" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E16" t="str">
-        <x:v>wave_plan.xlsx</x:v>
-      </x:c>
-      <x:c r="F16"/>
-      <x:c r="G16" t="str">
-        <x:v>map</x:v>
-      </x:c>
-      <x:c r="H16" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="I16" t="str">
-        <x:v>波次方案（演示20波，数值可由策划调整）</x:v>
-      </x:c>
-      <x:c r="J16"/>
-      <x:c r="K16"/>
-      <x:c r="L16"/>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <ns0:sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <ns0:cols>
+    <ns0:col min="2" max="2" width="20.380952835083008" customWidth="1"/>
+    <ns0:col min="3" max="3" width="15.571428298950195" customWidth="1"/>
+    <ns0:col min="4" max="4" width="32.42856979370117" customWidth="1"/>
+    <ns0:col min="5" max="5" width="24.380952835083008" customWidth="1"/>
+    <ns0:col min="6" max="9" width="18" customWidth="1"/>
+  </ns0:cols>
+  <ns0:sheetData>
+    <ns0:row r="1" s="1" customFormat="1">
+      <ns0:c r="A1" s="1" t="s">
+        <ns0:v>0</ns0:v>
+      </ns0:c>
+      <ns0:c r="B1" s="1" t="s">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="C1" s="1" t="s">
+        <ns0:v>2</ns0:v>
+      </ns0:c>
+      <ns0:c r="D1" s="1" t="s">
+        <ns0:v>3</ns0:v>
+      </ns0:c>
+      <ns0:c r="E1" s="1" t="s">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
+      <ns0:c r="F1" s="1" t="s">
+        <ns0:v>5</ns0:v>
+      </ns0:c>
+      <ns0:c r="G1" s="1" t="s">
+        <ns0:v>6</ns0:v>
+      </ns0:c>
+      <ns0:c r="H1" s="1" t="s">
+        <ns0:v>7</ns0:v>
+      </ns0:c>
+      <ns0:c r="I1" s="1" t="s">
+        <ns0:v>8</ns0:v>
+      </ns0:c>
+      <ns0:c r="J1" s="1" t="s">
+        <ns0:v>9</ns0:v>
+      </ns0:c>
+      <ns0:c r="K1" s="1" t="s">
+        <ns0:v>10</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="2" s="1" customFormat="1">
+      <ns0:c r="A2" s="1" t="s">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="B2" s="1" t="s">
+        <ns0:v>12</ns0:v>
+      </ns0:c>
+      <ns0:c r="C2" s="1" t="s">
+        <ns0:v>13</ns0:v>
+      </ns0:c>
+      <ns0:c r="D2" s="1" t="s">
+        <ns0:v>14</ns0:v>
+      </ns0:c>
+      <ns0:c r="E2" s="1" t="s">
+        <ns0:v>15</ns0:v>
+      </ns0:c>
+      <ns0:c r="F2" s="1" t="s">
+        <ns0:v>16</ns0:v>
+      </ns0:c>
+      <ns0:c r="G2" s="1" t="s">
+        <ns0:v>17</ns0:v>
+      </ns0:c>
+      <ns0:c r="H2" s="1" t="s">
+        <ns0:v>18</ns0:v>
+      </ns0:c>
+      <ns0:c r="I2" s="1" t="s">
+        <ns0:v>19</ns0:v>
+      </ns0:c>
+      <ns0:c r="K2" s="1" t="s">
+        <ns0:v>20</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="3" s="1" customFormat="1">
+      <ns0:c r="A3" s="1" t="s">
+        <ns0:v>11</ns0:v>
+      </ns0:c>
+      <ns0:c r="D3" s="1" t="s">
+        <ns0:v>21</ns0:v>
+      </ns0:c>
+      <ns0:c r="E3" s="1" t="s">
+        <ns0:v>22</ns0:v>
+      </ns0:c>
+      <ns0:c r="F3" s="1" t="s">
+        <ns0:v>23</ns0:v>
+      </ns0:c>
+      <ns0:c r="G3" s="1" t="s">
+        <ns0:v>24</ns0:v>
+      </ns0:c>
+      <ns0:c r="H3" s="1" t="s">
+        <ns0:v>25</ns0:v>
+      </ns0:c>
+      <ns0:c r="K3" s="1" t="s">
+        <ns0:v>26</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="4">
+      <ns0:c r="B4" t="s">
+        <ns0:v>27</ns0:v>
+      </ns0:c>
+      <ns0:c r="C4" t="s">
+        <ns0:v>28</ns0:v>
+      </ns0:c>
+      <ns0:c r="D4" t="b">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="E4" t="s">
+        <ns0:v>29</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="5">
+      <ns0:c r="B5" s="3" t="s">
+        <ns0:v>30</ns0:v>
+      </ns0:c>
+      <ns0:c r="C5" s="3" t="s">
+        <ns0:v>31</ns0:v>
+      </ns0:c>
+      <ns0:c r="D5" s="3" t="b">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="E5" s="3" t="s">
+        <ns0:v>32</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="6">
+      <ns0:c r="A6"/>
+      <ns0:c r="B6" t="str">
+        <ns0:v>robot.TbRobot</ns0:v>
+      </ns0:c>
+      <ns0:c r="C6" t="str">
+        <ns0:v>Robot</ns0:v>
+      </ns0:c>
+      <ns0:c r="D6" s="2" t="b">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="E6" t="str">
+        <ns0:v>robot.xlsx</ns0:v>
+      </ns0:c>
+      <ns0:c r="F6"/>
+      <ns0:c r="G6" t="str">
+        <ns0:v>map</ns0:v>
+      </ns0:c>
+      <ns0:c r="H6" t="str">
+        <ns0:v>c</ns0:v>
+      </ns0:c>
+      <ns0:c r="I6" t="str">
+        <ns0:v>机器人</ns0:v>
+      </ns0:c>
+      <ns0:c r="J6"/>
+      <ns0:c r="K6"/>
+    </ns0:row>
+    <ns0:row r="7">
+      <ns0:c r="A7"/>
+      <ns0:c r="B7" t="str">
+        <ns0:v>robot.TbRobotShape</ns0:v>
+      </ns0:c>
+      <ns0:c r="C7" t="str">
+        <ns0:v>RobotShape</ns0:v>
+      </ns0:c>
+      <ns0:c r="D7" s="2" t="b">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="E7" t="str">
+        <ns0:v>robot_shape.xlsx</ns0:v>
+      </ns0:c>
+      <ns0:c r="F7"/>
+      <ns0:c r="G7" t="str">
+        <ns0:v>map</ns0:v>
+      </ns0:c>
+      <ns0:c r="H7" t="str">
+        <ns0:v>c</ns0:v>
+      </ns0:c>
+      <ns0:c r="I7" t="str">
+        <ns0:v>机器人占格形状</ns0:v>
+      </ns0:c>
+      <ns0:c r="J7"/>
+      <ns0:c r="K7"/>
+    </ns0:row>
+    <ns0:row r="8">
+      <ns0:c r="A8"/>
+      <ns0:c r="B8" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">drop.TbDrop</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C8" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">Drop</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D8" s="2" t="b">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="E8" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">drop.xlsx</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F8"/>
+      <ns0:c r="G8" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">map</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H8" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">c</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I8" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">掉落配置</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J8"/>
+      <ns0:c r="K8"/>
+    </ns0:row>
+    <ns0:row r="9" ht="24" customHeight="1">
+      <ns0:c r="A9" s="1"/>
+      <ns0:c r="B9" s="1" t="str">
+        <ns0:v>glass.TbGlass</ns0:v>
+      </ns0:c>
+      <ns0:c r="C9" s="1" t="str">
+        <ns0:v>Glass</ns0:v>
+      </ns0:c>
+      <ns0:c r="D9" s="1" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="E9" s="1" t="str">
+        <ns0:v>glass.xlsx</ns0:v>
+      </ns0:c>
+      <ns0:c r="F9" s="1"/>
+      <ns0:c r="G9" s="1" t="str">
+        <ns0:v>map</ns0:v>
+      </ns0:c>
+      <ns0:c r="H9" s="1" t="str">
+        <ns0:v>c</ns0:v>
+      </ns0:c>
+      <ns0:c r="I9" s="1" t="str">
+        <ns0:v>玻璃配置</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="10" ht="24" customHeight="1">
+      <ns0:c r="A10" s="1"/>
+      <ns0:c r="B10" s="1" t="str">
+        <ns0:v>board.TbBoardLayout</ns0:v>
+      </ns0:c>
+      <ns0:c r="C10" s="1" t="str">
+        <ns0:v>BoardLayout</ns0:v>
+      </ns0:c>
+      <ns0:c r="D10" s="1" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="E10" s="1" t="str">
+        <ns0:v>board_layout.xlsx</ns0:v>
+      </ns0:c>
+      <ns0:c r="F10" s="1"/>
+      <ns0:c r="G10" s="1" t="str">
+        <ns0:v>map</ns0:v>
+      </ns0:c>
+      <ns0:c r="H10" s="1" t="str">
+        <ns0:v>c</ns0:v>
+      </ns0:c>
+      <ns0:c r="I10" s="1" t="str">
+        <ns0:v>棋盘布局配置</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="11">
+      <ns0:c r="A11"/>
+      <ns0:c r="B11" t="str">
+        <ns0:v>enemy.TbEnemy</ns0:v>
+      </ns0:c>
+      <ns0:c r="C11" t="str">
+        <ns0:v>Enemy</ns0:v>
+      </ns0:c>
+      <ns0:c r="D11" s="2" t="b">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="E11" t="str">
+        <ns0:v>enemy.xlsx</ns0:v>
+      </ns0:c>
+      <ns0:c r="F11"/>
+      <ns0:c r="G11" t="str">
+        <ns0:v>map</ns0:v>
+      </ns0:c>
+      <ns0:c r="H11" t="str">
+        <ns0:v>c</ns0:v>
+      </ns0:c>
+      <ns0:c r="I11" t="str">
+        <ns0:v>敌人配置</ns0:v>
+      </ns0:c>
+      <ns0:c r="J11"/>
+      <ns0:c r="K11"/>
+    </ns0:row>
+    <ns0:row r="12">
+      <ns0:c r="B12" t="str">
+        <ns0:v>tower.TbTower</ns0:v>
+      </ns0:c>
+      <ns0:c r="C12" t="str">
+        <ns0:v>Tower</ns0:v>
+      </ns0:c>
+      <ns0:c r="D12" s="2" t="b">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="E12" t="str">
+        <ns0:v>tower.xlsx</ns0:v>
+      </ns0:c>
+      <ns0:c r="F12"/>
+      <ns0:c r="G12" t="str">
+        <ns0:v>map</ns0:v>
+      </ns0:c>
+      <ns0:c r="H12" t="str">
+        <ns0:v>c</ns0:v>
+      </ns0:c>
+      <ns0:c r="I12" t="str">
+        <ns0:v>防御塔配置</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="13">
+      <ns0:c r="B13" t="str">
+        <ns0:v>wave.TbWaveSpawn</ns0:v>
+      </ns0:c>
+      <ns0:c r="C13" t="str">
+        <ns0:v>WaveSpawn</ns0:v>
+      </ns0:c>
+      <ns0:c r="D13" s="2" t="b">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="E13" t="str">
+        <ns0:v>wave_spawn.xlsx</ns0:v>
+      </ns0:c>
+      <ns0:c r="F13"/>
+      <ns0:c r="G13" t="str">
+        <ns0:v>map</ns0:v>
+      </ns0:c>
+      <ns0:c r="H13" t="str">
+        <ns0:v>c</ns0:v>
+      </ns0:c>
+      <ns0:c r="I13" t="str">
+        <ns0:v>波次出兵配置</ns0:v>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="14" ht="42" customHeight="1">
+      <ns0:c r="A14"/>
+      <ns0:c r="B14" t="str">
+        <ns0:v>item.TbItemBase</ns0:v>
+      </ns0:c>
+      <ns0:c r="C14" t="str">
+        <ns0:v>ItemBase</ns0:v>
+      </ns0:c>
+      <ns0:c r="D14" t="b">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="E14" t="str">
+        <ns0:v>item_base.xlsx</ns0:v>
+      </ns0:c>
+      <ns0:c r="F14"/>
+      <ns0:c r="G14" t="str">
+        <ns0:v>map</ns0:v>
+      </ns0:c>
+      <ns0:c r="H14" t="str">
+        <ns0:v>c</ns0:v>
+      </ns0:c>
+      <ns0:c r="I14" t="str">
+        <ns0:v>道具基础表</ns0:v>
+      </ns0:c>
+      <ns0:c r="J14"/>
+      <ns0:c r="K14"/>
+    </ns0:row>
+    <ns0:row r="15" ht="42" customHeight="1">
+      <ns0:c r="A15"/>
+      <ns0:c r="B15" t="str">
+        <ns0:v>settlement.TbResultAward</ns0:v>
+      </ns0:c>
+      <ns0:c r="C15" t="str">
+        <ns0:v>ResultAward</ns0:v>
+      </ns0:c>
+      <ns0:c r="D15" t="b">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="E15" t="str">
+        <ns0:v>result_award.xlsx</ns0:v>
+      </ns0:c>
+      <ns0:c r="F15"/>
+      <ns0:c r="G15" t="str">
+        <ns0:v>map</ns0:v>
+      </ns0:c>
+      <ns0:c r="H15" t="str">
+        <ns0:v>c</ns0:v>
+      </ns0:c>
+      <ns0:c r="I15" t="str">
+        <ns0:v>结算奖励表</ns0:v>
+      </ns0:c>
+      <ns0:c r="J15"/>
+      <ns0:c r="K15"/>
+    </ns0:row>
+    <ns0:row r="16">
+      <ns0:c r="A16"/>
+      <ns0:c r="B16" t="str">
+        <ns0:v>wave.TbWavePlan</ns0:v>
+      </ns0:c>
+      <ns0:c r="C16" t="str">
+        <ns0:v>WavePlan</ns0:v>
+      </ns0:c>
+      <ns0:c r="D16" s="2" t="b">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="E16" t="str">
+        <ns0:v>wave_plan.xlsx</ns0:v>
+      </ns0:c>
+      <ns0:c r="F16"/>
+      <ns0:c r="G16" t="str">
+        <ns0:v>map</ns0:v>
+      </ns0:c>
+      <ns0:c r="H16" t="str">
+        <ns0:v>c</ns0:v>
+      </ns0:c>
+      <ns0:c r="I16" t="str">
+        <ns0:v>波次方案（演示20波，数值可由策划调整）</ns0:v>
+      </ns0:c>
+      <ns0:c r="J16"/>
+      <ns0:c r="K16"/>
+      <ns0:c r="L16"/>
+    </ns0:row>
+    <ns0:row r="17">
+      <ns0:c r="B17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>skill.TbSkill</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Skill</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>1</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>skill.xlsx</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>map</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>c</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I17" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Skill</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="18">
+      <ns0:c r="B18" t="inlineStr">
+        <ns0:is>
+          <ns0:t>skill.TbSkillLevel</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C18" t="inlineStr">
+        <ns0:is>
+          <ns0:t>SkillLevel</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D18" t="inlineStr">
+        <ns0:is>
+          <ns0:t>1</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E18" t="inlineStr">
+        <ns0:is>
+          <ns0:t>skill_level.xlsx</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G18" t="inlineStr">
+        <ns0:is>
+          <ns0:t>map</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H18" t="inlineStr">
+        <ns0:is>
+          <ns0:t>c</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I18" t="inlineStr">
+        <ns0:is>
+          <ns0:t>SkillLevel</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="19">
+      <ns0:c r="B19" t="inlineStr">
+        <ns0:is>
+          <ns0:t>buff.TbBuff</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C19" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Buff</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D19" t="inlineStr">
+        <ns0:is>
+          <ns0:t>1</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E19" t="inlineStr">
+        <ns0:is>
+          <ns0:t>buff.xlsx</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G19" t="inlineStr">
+        <ns0:is>
+          <ns0:t>map</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H19" t="inlineStr">
+        <ns0:is>
+          <ns0:t>c</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I19" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Buff</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+  </ns0:sheetData>
+  <ns0:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</ns0:worksheet>
 </file>